--- a/be/excel-example/mau_danh_sach_tai_san.xlsx
+++ b/be/excel-example/mau_danh_sach_tai_san.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\quan-ly-kho-quan-nhu\be\excel-example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tan\Downloads\quan-ly-kho-quan-nhu\be\excel-example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBFD44C-C188-40B4-B218-4866B520C630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A85FAD3-5DA5-4672-BEF1-F3D27B6E5A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5184" yWindow="2136" windowWidth="13008" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách tài sản" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Mã tài sản</t>
   </si>
@@ -46,22 +46,16 @@
     <t>Ngày sản xuất</t>
   </si>
   <si>
-    <t>Áo khoácmùa hè</t>
-  </si>
-  <si>
-    <t>xe tải 1</t>
-  </si>
-  <si>
-    <t>Súng uzi</t>
-  </si>
-  <si>
-    <t>DP-0006</t>
-  </si>
-  <si>
-    <t>VK-0004</t>
-  </si>
-  <si>
-    <t>PT-0005</t>
+    <t xml:space="preserve">Áo khoác quân phục mùa đông	</t>
+  </si>
+  <si>
+    <t>PT-0001</t>
+  </si>
+  <si>
+    <t>Xe tải ZIL-130</t>
+  </si>
+  <si>
+    <t>DP-0004</t>
   </si>
 </sst>
 </file>
@@ -72,7 +66,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -102,7 +96,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -403,19 +397,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.3984375" customWidth="1"/>
-    <col min="2" max="2" width="16.8984375" customWidth="1"/>
-    <col min="3" max="3" width="35.8984375" customWidth="1"/>
-    <col min="4" max="4" width="23.69921875" customWidth="1"/>
-    <col min="5" max="5" width="24.3984375" customWidth="1"/>
-    <col min="6" max="6" width="16.796875" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" customWidth="1"/>
-    <col min="8" max="8" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="35.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -441,7 +435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -464,12 +458,12 @@
         <v>46433</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>50</v>
@@ -487,28 +481,10 @@
         <v>47766</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>40</v>
-      </c>
-      <c r="E4">
-        <v>100000</v>
-      </c>
-      <c r="F4" s="1">
-        <v>44844</v>
-      </c>
-      <c r="G4" s="1">
-        <v>46305</v>
-      </c>
-      <c r="H4" s="1">
-        <v>47766</v>
-      </c>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/be/excel-example/mau_danh_sach_tai_san.xlsx
+++ b/be/excel-example/mau_danh_sach_tai_san.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tan\Downloads\quan-ly-kho-quan-nhu\be\excel-example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\quan_ly_kho\be\excel-example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A85FAD3-5DA5-4672-BEF1-F3D27B6E5A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559062EF-2F89-4193-B529-339F1112473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5184" yWindow="2136" windowWidth="13008" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2508" yWindow="2508" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Danh sách tài sản" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Mã tài sản</t>
   </si>
@@ -49,13 +49,13 @@
     <t xml:space="preserve">Áo khoác quân phục mùa đông	</t>
   </si>
   <si>
-    <t>PT-0001</t>
-  </si>
-  <si>
     <t>Xe tải ZIL-130</t>
   </si>
   <si>
-    <t>DP-0004</t>
+    <t>VK-0001</t>
+  </si>
+  <si>
+    <t>BATCH-1-20260629-YAD784</t>
   </si>
 </sst>
 </file>
@@ -436,8 +436,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -460,10 +463,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
       </c>
       <c r="D3">
         <v>50</v>
